--- a/data/trans_dic/IP31KM09_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,12; 86,38</t>
+          <t>75,06; 91,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,48; 91,45</t>
+          <t>69,35; 87,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,87; 87,66</t>
+          <t>75,72; 87,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,51; 94,79</t>
+          <t>89,5; 96,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,07; 96,2</t>
+          <t>86,07; 94,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,24; 94,6</t>
+          <t>89,81; 94,58</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,68; 97,43</t>
+          <t>91,6; 97,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,04; 97,73</t>
+          <t>91,24; 97,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,07; 96,86</t>
+          <t>92,77; 96,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,15; 97,33</t>
+          <t>81,86; 95,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,5; 95,34</t>
+          <t>91,39; 96,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,38; 95,55</t>
+          <t>87,12; 95,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,03; 94,62</t>
+          <t>88,43; 94,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,42; 94,63</t>
+          <t>90,78; 94,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,92; 94,01</t>
+          <t>90,52; 94,02</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>33920</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75192</t>
+          <t>65794</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32135; 40163</t>
+          <t>28100; 34266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33274; 41415</t>
+          <t>29598; 37188</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68714; 80456</t>
+          <t>60660; 70185</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>145902</t>
+          <t>146896</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>170394</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316297</t>
+          <t>279610</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139397; 151000</t>
+          <t>140549; 150794</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163889; 175039</t>
+          <t>125247; 137356</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307954; 322837</t>
+          <t>271718; 286155</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>221</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>164505</t>
+          <t>190281</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202525</t>
+          <t>165762</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367031</t>
+          <t>356043</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>158679; 168621</t>
+          <t>183315; 195193</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>195572; 207675</t>
+          <t>159368; 169823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358851; 373445</t>
+          <t>347706; 362592</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>322</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>260120</t>
+          <t>267806</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>278046</t>
+          <t>240752</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538167</t>
+          <t>508558</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>252724; 266941</t>
+          <t>239207; 278894</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>233323; 290771</t>
+          <t>233352; 246434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>500349; 553471</t>
+          <t>477025; 520553</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>844</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>607377</t>
+          <t>636857</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>594531; 618007</t>
+          <t>607353; 650829</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>643635; 704732</t>
+          <t>561227; 582761</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1256992; 1314187</t>
+          <t>1181271; 1226927</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM09_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>75,06; 91,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>69,35; 87,13</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75,72; 87,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>89,5; 96,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86,07; 94,39</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>89,81; 94,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>91,6; 97,54</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>91,24; 97,22</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>92,77; 96,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>81,86; 95,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>91,39; 96,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87,12; 95,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>88,43; 94,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>90,78; 94,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>90,52; 94,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8514559926034521</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7947363885321053</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8212393256555304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>31874</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33920</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65794</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7506228601797333</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6934693204879202</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7571562385316692</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>28100; 34266</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29598; 37188</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60660; 70185</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9153556585230536</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8712941416922542</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8760405262853401</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9353961826144206</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9120076369432778</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9241473399267863</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>146896</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>132714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>279610</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8949741091365448</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8606976933376284</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8980628962040829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>140549; 150794</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125247; 137356</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>271718; 286155</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9602117240071089</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9439133803668984</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9457782573271308</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9508042664699298</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9489905306771919</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9499589864197726</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>190281</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>165762</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>356043</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9159961977441617</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9123828520545564</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9277151389364352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>183315; 195193</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>159368; 169823</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>347706; 362592</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9753515983785984</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9722412084784871</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9674330768302764</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9164491235387895</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9428796227592284</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9287741896878414</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>267806</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>240752</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>508558</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8185822288985073</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9138973312592749</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8711862049042324</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>239207; 278894</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>233352; 246434</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>477025; 520553</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9543953933480388</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9651310959190516</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9506803748773528</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9272492928201883</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9271116768121139</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9271841026066828</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>636857</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>573148</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1210004</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8842917752124185</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9078286603310789</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9051669748772317</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>607353; 650829</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>561227; 582761</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1181271; 1226927</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9475922409419725</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9426622292671428</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9401513816581489</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>31874</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>33920</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>65794</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>28100</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>29598</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>60660</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>34266</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>37188</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>70185</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>258</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>146896</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>132714</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>279610</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>140549</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>125247</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>271718</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>150794</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>137356</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>286155</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>190281</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>165762</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>356043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>183315</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>159368</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>347706</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>195193</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>169823</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>362592</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>321</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>322</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>267806</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>240752</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>508558</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>239207</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>233352</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>477025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>278894</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>246434</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>520553</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>879</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>844</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>636857</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>573148</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1210004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>607353</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>561227</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1181271</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>650829</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>582761</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1226927</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>